--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -25,39 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
     <t>2026-06-23</t>
   </si>
   <si>
@@ -293,6 +260,36 @@
   </si>
   <si>
     <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
   </si>
   <si>
     <t>Issue</t>
@@ -351,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -373,7 +370,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +392,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>52.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +414,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>54.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>54.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +436,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>56.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +447,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +458,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="13">
@@ -505,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +535,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +546,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +568,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +601,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +612,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>66.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +656,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>66.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +667,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +678,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +689,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +700,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +733,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>68.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +744,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>68.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>69.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +766,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>70.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +777,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +788,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>72.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +799,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +810,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>71.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +821,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +832,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +843,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +854,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +865,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +909,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +931,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="54">
@@ -956,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +964,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +997,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1008,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1041,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1052,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1074,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1085,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1096,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1107,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1118,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="71">
@@ -1143,7 +1140,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1151,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1173,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="76">
@@ -1198,7 +1195,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1206,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1217,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1228,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1239,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1250,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1261,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1272,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1283,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="86">
@@ -1308,7 +1305,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="88">
@@ -1330,7 +1327,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,18 +1338,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>54.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
   </sheetData>
@@ -1367,13 +1353,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1388,13 +1374,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -25,24 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
     <t>2026-06-29</t>
   </si>
   <si>
@@ -290,6 +272,27 @@
   </si>
   <si>
     <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
   </si>
   <si>
     <t>Issue</t>
@@ -348,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -370,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="4">
@@ -403,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="6">
@@ -414,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="7">
@@ -425,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="8">
@@ -436,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="10">
@@ -458,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="11">
@@ -469,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="12">
@@ -480,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="13">
@@ -491,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="14">
@@ -502,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="15">
@@ -513,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="16">
@@ -524,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="17">
@@ -535,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="18">
@@ -546,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="19">
@@ -557,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="20">
@@ -568,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="21">
@@ -579,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="22">
@@ -590,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="24">
@@ -612,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="25">
@@ -623,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="26">
@@ -634,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="28">
@@ -656,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="29">
@@ -667,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="30">
@@ -678,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="31">
@@ -689,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="33">
@@ -711,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="34">
@@ -722,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="35">
@@ -733,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="36">
@@ -744,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>67.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="38">
@@ -766,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="39">
@@ -777,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="40">
@@ -788,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="41">
@@ -799,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="42">
@@ -810,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="43">
@@ -887,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="50">
@@ -898,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="51">
@@ -909,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="52">
@@ -920,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="53">
@@ -931,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="54">
@@ -942,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="55">
@@ -953,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="56">
@@ -964,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="57">
@@ -975,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="58">
@@ -986,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="59">
@@ -997,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="60">
@@ -1008,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="61">
@@ -1041,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="64">
@@ -1052,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="65">
@@ -1063,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="66">
@@ -1074,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="68">
@@ -1096,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="69">
@@ -1118,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="71">
@@ -1140,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="73">
@@ -1151,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="74">
@@ -1162,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="75">
@@ -1173,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="76">
@@ -1184,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="77">
@@ -1195,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="78">
@@ -1228,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="81">
@@ -1239,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="82">
@@ -1250,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="83">
@@ -1261,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="84">
@@ -1272,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="85">
@@ -1283,7 +1286,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="86">
@@ -1327,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="90">
@@ -1338,7 +1341,18 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>54.0</v>
       </c>
     </row>
   </sheetData>
@@ -1353,13 +1367,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1374,13 +1388,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,33 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
     <t>2026-07-08</t>
   </si>
   <si>
@@ -293,6 +266,33 @@
   </si>
   <si>
     <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
   </si>
   <si>
     <t>Issue</t>
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>71.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="32">
@@ -703,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="37">
@@ -791,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="54">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="61">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="71">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="80">
@@ -1231,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="81">
@@ -1242,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="83">
@@ -1264,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="84">
@@ -1275,7 +1275,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="85">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="89">

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -25,30 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>2026-07-12</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
     <t>2026-07-16</t>
   </si>
   <si>
@@ -293,6 +269,27 @@
   </si>
   <si>
     <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>Issue</t>
@@ -351,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -373,7 +370,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +392,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +414,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +436,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +447,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +458,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="11">
@@ -483,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +491,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="14">
@@ -505,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="17">
@@ -538,7 +535,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="18">
@@ -549,7 +546,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="19">
@@ -560,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>69.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="20">
@@ -571,7 +568,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="21">
@@ -582,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +601,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +612,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="28">
@@ -703,7 +700,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="33">
@@ -714,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="34">
@@ -725,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="35">
@@ -736,7 +733,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +744,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="38">
@@ -769,7 +766,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +777,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="40">
@@ -791,7 +788,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="41">
@@ -802,7 +799,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="42">
@@ -813,7 +810,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="43">
@@ -824,7 +821,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="44">
@@ -835,7 +832,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +843,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +854,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="47">
@@ -868,7 +865,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="49">
@@ -890,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="50">
@@ -901,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="51">
@@ -912,7 +909,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="52">
@@ -923,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="53">
@@ -956,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +964,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="57">
@@ -978,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="58">
@@ -989,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="59">
@@ -1000,7 +997,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="60">
@@ -1011,7 +1008,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="61">
@@ -1022,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1041,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1052,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1074,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1085,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="68">
@@ -1099,7 +1096,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="69">
@@ -1110,7 +1107,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1118,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="71">
@@ -1143,7 +1140,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="73">
@@ -1154,7 +1151,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1173,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1184,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="77">
@@ -1220,7 +1217,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="80">
@@ -1275,7 +1272,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="85">
@@ -1286,7 +1283,7 @@
         <v>0.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="86">
@@ -1297,7 +1294,7 @@
         <v>0.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1305,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1316,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1327,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,18 +1338,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>54.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B91" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C91" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
   </sheetData>
@@ -1367,13 +1353,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1388,13 +1374,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -25,24 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
     <t>2026-07-22</t>
   </si>
   <si>
@@ -290,6 +272,27 @@
   </si>
   <si>
     <t>2026-10-12</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
   </si>
   <si>
     <t>Issue</t>
@@ -348,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -370,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="4">
@@ -392,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="6">
@@ -414,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="7">
@@ -425,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="8">
@@ -436,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="10">
@@ -458,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="11">
@@ -469,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="12">
@@ -480,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="13">
@@ -491,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>67.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="14">
@@ -502,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="15">
@@ -513,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="16">
@@ -524,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="17">
@@ -535,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="18">
@@ -546,7 +549,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="19">
@@ -557,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="20">
@@ -634,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="28">
@@ -656,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="29">
@@ -667,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="30">
@@ -678,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="31">
@@ -689,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="32">
@@ -700,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="33">
@@ -711,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="34">
@@ -722,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="35">
@@ -733,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="36">
@@ -744,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="38">
@@ -788,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="41">
@@ -799,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="42">
@@ -810,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="43">
@@ -821,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="44">
@@ -832,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="45">
@@ -843,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="46">
@@ -865,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="48">
@@ -887,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="50">
@@ -898,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="51">
@@ -909,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="52">
@@ -920,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="53">
@@ -931,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="54">
@@ -942,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="55">
@@ -975,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="58">
@@ -986,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="59">
@@ -997,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="60">
@@ -1008,7 +1011,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="61">
@@ -1019,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="62">
@@ -1030,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="63">
@@ -1074,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="68">
@@ -1096,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="69">
@@ -1107,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="70">
@@ -1118,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="71">
@@ -1140,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="73">
@@ -1195,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="78">
@@ -1206,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="79">
@@ -1217,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="80">
@@ -1228,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="81">
@@ -1239,7 +1242,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="82">
@@ -1250,7 +1253,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="83">
@@ -1261,7 +1264,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="84">
@@ -1338,6 +1341,17 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
         <v>55.0</v>
       </c>
     </row>
@@ -1353,13 +1367,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1374,13 +1388,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,12 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
     <t>2026-07-24</t>
   </si>
   <si>
@@ -293,6 +287,12 @@
   </si>
   <si>
     <t>2026-10-19</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
   </si>
   <si>
     <t>Issue</t>
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>71.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="8">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>66.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>66.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>63.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="13">
@@ -494,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="14">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="25">
@@ -626,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="27">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="31">
@@ -692,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="32">
@@ -769,7 +769,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="39">
@@ -780,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="40">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="46">
@@ -868,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="48">
@@ -879,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="49">
@@ -956,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="56">
@@ -967,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="57">
@@ -1055,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="66">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="71">
@@ -1132,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="72">
@@ -1143,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="73">
@@ -1187,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="78">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Breadcrumbs.xlsx
+++ b/gsc-export/Breadcrumbs.xlsx
@@ -25,15 +25,6 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>2026-07-26</t>
-  </si>
-  <si>
     <t>2026-07-27</t>
   </si>
   <si>
@@ -293,6 +284,15 @@
   </si>
   <si>
     <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
+  </si>
+  <si>
+    <t>2026-10-24</t>
   </si>
   <si>
     <t>Issue</t>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="3">
@@ -384,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>69.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="5">
@@ -406,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>66.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="7">
@@ -428,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>66.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="8">
@@ -439,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>66.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="9">
@@ -450,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="10">
@@ -461,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="11">
@@ -472,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="12">
@@ -582,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="23">
@@ -604,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="24">
@@ -615,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="25">
@@ -637,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="27">
@@ -648,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="28">
@@ -659,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="29">
@@ -670,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="30">
@@ -736,7 +736,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="37">
@@ -758,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="38">
@@ -813,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="43">
@@ -835,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="45">
@@ -846,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="46">
@@ -857,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="47">
@@ -923,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="53">
@@ -934,7 +934,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="54">
@@ -945,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="55">
@@ -1022,7 +1022,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="62">
@@ -1033,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="63">
@@ -1044,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="64">
@@ -1077,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="67">
@@ -1088,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="68">
@@ -1110,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="71">
@@ -1154,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="74">
@@ -1165,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="75">
@@ -1176,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="76">
@@ -1308,7 +1308,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="88">
@@ -1319,7 +1319,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="89">
@@ -1330,7 +1330,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="90">
@@ -1341,7 +1341,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>56.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="91">
@@ -1352,7 +1352,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>56.0</v>
+        <v>52.0</v>
       </c>
     </row>
   </sheetData>
